--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.3_Requirements_Register_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.3_Requirements_Register_20260208.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="3">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="R3" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="4">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="5">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="R5" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="6">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="7">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="R7" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="9">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="R9" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="10">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="11">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="R11" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="12">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
     <row r="13">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="R13" s="4" t="n">
-        <v>46061.49235408171</v>
+        <v>46061.51767418042</v>
       </c>
     </row>
   </sheetData>
